--- a/xls/square_12_tri3_18.xlsx
+++ b/xls/square_12_tri3_18.xlsx
@@ -482,13 +482,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-1.8944680494805612</v>
+        <v>-1.8944679934089752</v>
       </c>
       <c r="J18">
-        <v>-1.47698608873123</v>
+        <v>-1.4769860913689463</v>
       </c>
       <c r="K18">
-        <v>2.9681660824988336</v>
+        <v>2.9681660034563784</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.7070369391443461</v>
+        <v>-0.7070369258984434</v>
       </c>
       <c r="J19">
-        <v>-0.592702850143444</v>
+        <v>-0.5927028403186637</v>
       </c>
       <c r="K19">
-        <v>3.8326961596644606</v>
+        <v>3.8326961545894593</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.07116987819413607</v>
+        <v>-0.07116987781744406</v>
       </c>
       <c r="J20">
-        <v>-0.06583312850088195</v>
+        <v>-0.06583312814407657</v>
       </c>
       <c r="K20">
-        <v>3.7933448292735736</v>
+        <v>3.7933448270062673</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.0011994619336681662</v>
+        <v>-0.0011994619375373528</v>
       </c>
       <c r="J21">
-        <v>-0.0008584588470236584</v>
+        <v>-0.0008584588494399237</v>
       </c>
       <c r="K21">
-        <v>2.7725868354255154</v>
+        <v>2.7725868361153143</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00024952930500475096</v>
+        <v>-0.0002495293050120358</v>
       </c>
       <c r="J22">
-        <v>-0.00017690434573535522</v>
+        <v>-0.00017690434573757407</v>
       </c>
       <c r="K22">
-        <v>2.435283757979888</v>
+        <v>2.4352837582393247</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.003257564762786512</v>
+        <v>-0.0032575647485897667</v>
       </c>
       <c r="J23">
-        <v>-0.002258429683708149</v>
+        <v>-0.002258429674021188</v>
       </c>
       <c r="K23">
-        <v>2.9407428099038397</v>
+        <v>2.9407428084061693</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.00010172424593610792</v>
+        <v>-0.00010172424592853618</v>
       </c>
       <c r="J24">
-        <v>-8.013676148172724e-5</v>
+        <v>-8.013676147888195e-5</v>
       </c>
       <c r="K24">
-        <v>2.3162857414476976</v>
+        <v>2.3162857412751685</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.00010687473803841634</v>
+        <v>-0.00010687473805577851</v>
       </c>
       <c r="J25">
-        <v>-9.073479454171306e-5</v>
+        <v>-9.073479455285336e-5</v>
       </c>
       <c r="K25">
-        <v>2.3702360541009675</v>
+        <v>2.370236054020366</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00011891987782958463</v>
+        <v>-0.00011891987782997047</v>
       </c>
       <c r="J26">
-        <v>-9.419497239020288e-5</v>
+        <v>-9.419497239160146e-5</v>
       </c>
       <c r="K26">
-        <v>2.350019355987207</v>
+        <v>2.3500193560399483</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.00011018990280189494</v>
+        <v>-0.00011018990279041653</v>
       </c>
       <c r="J27">
-        <v>-7.875056839274698e-5</v>
+        <v>-7.875056838585079e-5</v>
       </c>
       <c r="K27">
-        <v>2.2743497577357767</v>
+        <v>2.274349757917111</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -835,10 +835,10 @@
         <v>-3.680848148695279e-5</v>
       </c>
       <c r="J28">
-        <v>-3.110814976295705e-5</v>
+        <v>-3.110814976290883e-5</v>
       </c>
       <c r="K28">
-        <v>2.1466122917290718</v>
+        <v>2.146612291775313</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-4.458404061711541e-6</v>
+        <v>-4.458404061663325e-6</v>
       </c>
       <c r="J29">
-        <v>-3.704555898286579e-6</v>
+        <v>-3.7045558981901457e-6</v>
       </c>
       <c r="K29">
-        <v>1.683533766905262</v>
+        <v>1.6835337669508212</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-3.164931624641417e-6</v>
+        <v>-3.16493162444855e-6</v>
       </c>
       <c r="J30">
         <v>-3.0502639037406785e-6</v>
       </c>
       <c r="K30">
-        <v>1.679822254222709</v>
+        <v>1.6798222542921604</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-1.8856902201217175e-6</v>
+        <v>-1.885690219928851e-6</v>
       </c>
       <c r="J31">
-        <v>-2.2805324675681784e-6</v>
+        <v>-2.280532467809262e-6</v>
       </c>
       <c r="K31">
-        <v>1.6603551589492427</v>
+        <v>1.6603551591091128</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -972,13 +972,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-7.769758839658604e-6</v>
+        <v>-7.769758839465734e-6</v>
       </c>
       <c r="J32">
         <v>-6.435667719944845e-6</v>
       </c>
       <c r="K32">
-        <v>1.7885606587370038</v>
+        <v>1.7885606585329852</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_18.xlsx
+++ b/xls/square_12_tri3_18.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>361</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1536</v>
+      </c>
+      <c r="I16">
+        <v>2.3827238335154655</v>
+      </c>
+      <c r="J16">
+        <v>-0.7738583242463503</v>
+      </c>
+      <c r="K16">
+        <v>3.0772538114259027</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>361</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>0.3388296981916242</v>
+      </c>
+      <c r="J17">
+        <v>-1.684518458319341</v>
+      </c>
+      <c r="K17">
+        <v>2.24414358052466</v>
+      </c>
+    </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>11</v>
